--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -14726,12 +14726,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14741,29 +14741,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14773,29 +14773,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -14817,17 +14817,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14837,29 +14837,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -14881,17 +14881,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14901,29 +14901,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14933,29 +14933,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -14977,17 +14977,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14997,29 +14997,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15029,29 +15029,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15061,29 +15061,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15105,17 +15105,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15125,29 +15125,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15157,29 +15157,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15189,29 +15189,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15221,29 +15221,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15253,29 +15253,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15285,29 +15285,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15317,29 +15317,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15349,29 +15349,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15381,29 +15381,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15413,29 +15413,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15445,29 +15445,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15477,29 +15477,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15509,29 +15509,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15541,7 +15541,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15553,17 +15553,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15573,29 +15573,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
@@ -15617,17 +15617,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15637,29 +15637,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15669,29 +15669,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15701,29 +15701,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15733,29 +15733,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15765,29 +15765,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15809,17 +15809,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15829,29 +15829,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15861,14 +15861,14 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -15878,12 +15878,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15893,29 +15893,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -15969,17 +15969,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16001,17 +16001,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16033,17 +16033,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16053,29 +16053,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16097,17 +16097,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16129,17 +16129,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16161,17 +16161,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16188,22 +16188,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16225,17 +16225,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16257,17 +16257,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16284,22 +16284,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16321,17 +16321,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16353,17 +16353,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16412,22 +16412,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16444,22 +16444,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16476,22 +16476,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16508,22 +16508,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16540,22 +16540,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16572,22 +16572,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16609,17 +16609,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16636,22 +16636,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16673,17 +16673,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16700,22 +16700,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16732,22 +16732,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16769,17 +16769,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16801,17 +16801,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16833,17 +16833,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16865,17 +16865,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16897,17 +16897,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16924,22 +16924,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16956,22 +16956,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -16988,22 +16988,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17025,17 +17025,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17084,22 +17084,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17116,22 +17116,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17148,22 +17148,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17180,22 +17180,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17217,17 +17217,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17244,22 +17244,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -17269,29 +17269,29 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -17301,29 +17301,29 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17333,29 +17333,29 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17377,17 +17377,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17397,29 +17397,29 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17429,29 +17429,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
     </row>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
     </row>
@@ -14721,17 +14721,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -14753,17 +14753,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14773,29 +14773,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14805,29 +14805,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14837,29 +14837,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -14881,17 +14881,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -14913,17 +14913,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14933,29 +14933,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -14977,17 +14977,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
@@ -15009,17 +15009,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15029,29 +15029,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15061,29 +15061,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15093,29 +15093,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -15164,22 +15164,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15189,29 +15189,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15221,29 +15221,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15253,29 +15253,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15297,17 +15297,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15317,29 +15317,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
@@ -15366,12 +15366,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15381,29 +15381,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15413,29 +15413,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15445,29 +15445,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15489,17 +15489,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15509,7 +15509,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
@@ -15580,22 +15580,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15605,29 +15605,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15654,12 +15654,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15708,22 +15708,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15733,29 +15733,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
@@ -15777,17 +15777,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15797,29 +15797,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15829,29 +15829,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15861,29 +15861,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
@@ -15932,22 +15932,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16001,17 +16001,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16021,29 +16021,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16065,17 +16065,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16085,29 +16085,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16156,22 +16156,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16188,22 +16188,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16220,22 +16220,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16257,17 +16257,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16284,22 +16284,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16353,17 +16353,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16385,17 +16385,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16412,22 +16412,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16444,22 +16444,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16508,22 +16508,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16545,17 +16545,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16572,22 +16572,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16609,17 +16609,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16636,22 +16636,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16668,22 +16668,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16700,22 +16700,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16732,22 +16732,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16764,22 +16764,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16801,17 +16801,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16828,22 +16828,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16865,17 +16865,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16897,17 +16897,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16929,17 +16929,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16961,17 +16961,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -16988,22 +16988,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17020,22 +17020,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17084,22 +17084,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17121,17 +17121,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17148,22 +17148,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17185,17 +17185,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17212,22 +17212,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17244,22 +17244,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -17269,29 +17269,29 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
@@ -17313,17 +17313,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17333,29 +17333,29 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17377,17 +17377,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17397,29 +17397,29 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17429,29 +17429,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
     </row>
@@ -14716,22 +14716,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14741,29 +14741,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14773,29 +14773,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14805,29 +14805,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14837,29 +14837,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
@@ -14881,17 +14881,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14901,29 +14901,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
@@ -14972,22 +14972,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14997,29 +14997,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15041,17 +15041,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15061,29 +15061,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15093,29 +15093,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15125,29 +15125,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15169,17 +15169,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15189,29 +15189,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15221,29 +15221,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15265,17 +15265,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15285,29 +15285,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15317,29 +15317,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15349,29 +15349,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15381,29 +15381,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15413,29 +15413,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15445,29 +15445,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15477,29 +15477,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15509,29 +15509,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15541,29 +15541,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15573,29 +15573,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15605,29 +15605,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15637,29 +15637,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15681,17 +15681,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15701,29 +15701,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
@@ -15745,17 +15745,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15765,29 +15765,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15797,29 +15797,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15829,29 +15829,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15861,29 +15861,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15893,29 +15893,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -15937,17 +15937,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -15969,17 +15969,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16001,17 +16001,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16021,29 +16021,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16053,29 +16053,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16097,17 +16097,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16124,22 +16124,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16156,22 +16156,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16193,17 +16193,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16220,22 +16220,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16257,17 +16257,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16289,17 +16289,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16321,17 +16321,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16353,17 +16353,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16380,22 +16380,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16417,17 +16417,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16449,17 +16449,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16476,22 +16476,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16508,22 +16508,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16545,17 +16545,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16572,22 +16572,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16609,17 +16609,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16641,17 +16641,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16668,22 +16668,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16705,17 +16705,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16732,22 +16732,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16764,22 +16764,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16828,22 +16828,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16860,22 +16860,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16897,17 +16897,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16924,22 +16924,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16961,17 +16961,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -16988,22 +16988,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17020,22 +17020,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17084,22 +17084,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17121,17 +17121,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17153,17 +17153,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17212,7 +17212,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -17222,12 +17222,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17308,22 +17308,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
@@ -17345,17 +17345,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -17377,17 +17377,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17436,22 +17436,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -14716,22 +14716,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -14753,17 +14753,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14773,29 +14773,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14805,29 +14805,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14837,29 +14837,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14869,29 +14869,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14901,29 +14901,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14933,29 +14933,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14965,29 +14965,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14997,29 +14997,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15029,29 +15029,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15073,17 +15073,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
@@ -15105,17 +15105,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15125,29 +15125,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15157,29 +15157,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15189,29 +15189,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15221,7 +15221,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15233,17 +15233,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15253,29 +15253,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15285,29 +15285,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15329,17 +15329,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15349,29 +15349,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15381,29 +15381,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -15452,22 +15452,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15477,29 +15477,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15509,29 +15509,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15541,29 +15541,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15573,29 +15573,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15622,12 +15622,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15637,29 +15637,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15669,29 +15669,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15701,29 +15701,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15733,29 +15733,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15777,17 +15777,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15797,29 +15797,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15829,29 +15829,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15861,29 +15861,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15893,29 +15893,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -15937,17 +15937,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -15969,17 +15969,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15989,29 +15989,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16033,17 +16033,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16053,29 +16053,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16085,29 +16085,29 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16124,22 +16124,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16156,22 +16156,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16193,17 +16193,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16220,22 +16220,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16252,22 +16252,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16284,22 +16284,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16321,17 +16321,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16353,17 +16353,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16380,22 +16380,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16417,17 +16417,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16449,17 +16449,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16481,17 +16481,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16508,22 +16508,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16545,17 +16545,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16577,17 +16577,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16609,17 +16609,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16641,17 +16641,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16668,22 +16668,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16705,17 +16705,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16732,22 +16732,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16764,22 +16764,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16796,22 +16796,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16828,22 +16828,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16860,22 +16860,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16897,17 +16897,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16924,22 +16924,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16961,17 +16961,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -16988,22 +16988,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17020,22 +17020,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17084,22 +17084,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17121,17 +17121,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17148,22 +17148,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17185,17 +17185,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17212,22 +17212,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17308,22 +17308,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17333,29 +17333,29 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -17365,29 +17365,29 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
@@ -17409,17 +17409,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17429,29 +17429,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
     </row>
@@ -14721,17 +14721,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14741,29 +14741,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14773,29 +14773,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14805,29 +14805,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14837,29 +14837,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14869,29 +14869,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14901,29 +14901,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -14945,17 +14945,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14965,29 +14965,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14997,29 +14997,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15029,29 +15029,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15061,29 +15061,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15105,17 +15105,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15125,29 +15125,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15169,17 +15169,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15189,29 +15189,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15221,29 +15221,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15253,29 +15253,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15297,17 +15297,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15317,29 +15317,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
@@ -15361,17 +15361,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15381,29 +15381,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15413,29 +15413,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15445,29 +15445,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15541,29 +15541,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15573,29 +15573,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15605,29 +15605,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15637,29 +15637,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15669,29 +15669,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15701,29 +15701,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15733,29 +15733,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15765,29 +15765,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15797,29 +15797,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15841,17 +15841,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
@@ -15873,17 +15873,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
@@ -15905,17 +15905,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -15937,17 +15937,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15957,29 +15957,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16060,22 +16060,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16097,17 +16097,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16124,22 +16124,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16156,22 +16156,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16193,17 +16193,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16225,17 +16225,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16252,22 +16252,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16284,22 +16284,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16321,17 +16321,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16348,22 +16348,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16380,22 +16380,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16417,17 +16417,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16449,17 +16449,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16476,22 +16476,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16508,22 +16508,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16545,17 +16545,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16577,17 +16577,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16604,22 +16604,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16636,22 +16636,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16668,22 +16668,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16705,17 +16705,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16732,22 +16732,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16764,22 +16764,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16796,22 +16796,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16833,17 +16833,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16860,22 +16860,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16897,17 +16897,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16929,17 +16929,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16961,17 +16961,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -16993,17 +16993,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17020,22 +17020,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17089,17 +17089,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17121,17 +17121,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17148,22 +17148,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17180,22 +17180,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17217,17 +17217,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17308,22 +17308,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17333,29 +17333,29 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -17365,29 +17365,29 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17409,17 +17409,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17429,29 +17429,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
     </row>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
     </row>
@@ -14721,17 +14721,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -14753,17 +14753,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14773,29 +14773,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -14817,17 +14817,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
@@ -14849,17 +14849,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14869,29 +14869,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -14913,17 +14913,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14933,29 +14933,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14965,29 +14965,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14997,29 +14997,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15029,29 +15029,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15061,29 +15061,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15093,29 +15093,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15125,29 +15125,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15169,17 +15169,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15189,29 +15189,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15221,29 +15221,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15253,29 +15253,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15285,29 +15285,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15317,29 +15317,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15349,29 +15349,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15393,17 +15393,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15413,29 +15413,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15457,17 +15457,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15477,29 +15477,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15509,29 +15509,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15541,29 +15541,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15573,29 +15573,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15605,29 +15605,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15637,29 +15637,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15669,29 +15669,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15701,29 +15701,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15733,29 +15733,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15777,17 +15777,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15797,29 +15797,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15841,17 +15841,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
@@ -15900,22 +15900,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -15937,17 +15937,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15957,29 +15957,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15989,29 +15989,29 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16021,29 +16021,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16065,17 +16065,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16097,17 +16097,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16129,17 +16129,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16156,22 +16156,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16193,17 +16193,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16220,22 +16220,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16252,22 +16252,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16289,17 +16289,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16321,17 +16321,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16348,22 +16348,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16380,22 +16380,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16417,17 +16417,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16444,22 +16444,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16481,17 +16481,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16508,22 +16508,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16545,17 +16545,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16577,17 +16577,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16604,22 +16604,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16636,22 +16636,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16668,22 +16668,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16705,17 +16705,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16732,22 +16732,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16764,22 +16764,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16801,17 +16801,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16833,17 +16833,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16860,22 +16860,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16892,22 +16892,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16924,22 +16924,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16961,17 +16961,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -16993,17 +16993,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17020,22 +17020,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17057,17 +17057,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17089,17 +17089,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17121,17 +17121,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17148,22 +17148,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17180,22 +17180,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17217,17 +17217,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17244,22 +17244,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -17269,29 +17269,29 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -17301,29 +17301,29 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
@@ -17372,22 +17372,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
@@ -17409,17 +17409,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17429,29 +17429,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8712</v>
+        <v>8714</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8634</v>
+        <v>8636</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-78</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="3" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="3" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -6626,45 +6626,45 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D273" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E273" s="2" t="n">
-        <v>-1</v>
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D274" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E274" s="2" t="n">
-        <v>-1</v>
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E275" s="2" t="n">
         <v>-1</v>
@@ -6696,59 +6696,59 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="E276" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="D277" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="E277" s="3" t="n">
-        <v>0</v>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D277" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C278" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E278" s="3" t="n">
-        <v>0</v>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="D278" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="279">
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="E279" s="3" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E280" s="3" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E281" s="3" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E282" s="3" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E283" s="3" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E284" s="3" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="E285" s="3" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E286" s="3" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E287" s="3" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E288" s="3" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="E289" s="3" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E290" s="3" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E291" s="3" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E292" s="3" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E293" s="3" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E294" s="3" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E295" s="3" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E296" s="3" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E297" s="3" t="n">
         <v>0</v>
@@ -7158,59 +7158,59 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E298" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E299" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C298" s="3" t="n">
+      <c r="C300" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D298" s="3" t="n">
+      <c r="D300" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E298" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D299" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E299" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="D300" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E300" s="4" t="n">
-        <v>1</v>
+      <c r="E300" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -7221,14 +7221,14 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C301" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D301" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E301" s="4" t="n">
         <v>1</v>
@@ -7242,59 +7242,59 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C302" s="4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D302" s="4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E302" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="D303" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="E303" s="2" t="n">
-        <v>-2</v>
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D304" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="E304" s="2" t="n">
-        <v>-2</v>
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7305,17 +7305,17 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C305" s="2" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="306">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="307">
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>-1</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E308" s="2" t="n">
         <v>-1</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>-1</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>-1</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>-1</v>
@@ -7452,59 +7452,59 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="3" t="inlineStr">
+      <c r="A313" s="2" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C313" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D313" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E313" s="3" t="n">
-        <v>0</v>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D313" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="3" t="inlineStr">
+      <c r="A314" s="2" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D314" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E314" s="3" t="n">
-        <v>0</v>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="315">
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E315" s="3" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="D316" s="3" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="E316" s="3" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D317" s="3" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E317" s="3" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E318" s="3" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E319" s="3" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D320" s="3" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E320" s="3" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="D321" s="3" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="E321" s="3" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D322" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E322" s="3" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="E323" s="3" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E324" s="3" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E325" s="3" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E326" s="3" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D327" s="3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E327" s="3" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E328" s="3" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E329" s="3" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E330" s="3" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E331" s="3" t="n">
         <v>0</v>
@@ -7872,80 +7872,80 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D332" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D333" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C332" s="3" t="n">
+      <c r="C334" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D332" s="3" t="n">
+      <c r="D334" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E332" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="4" t="inlineStr">
+      <c r="E334" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B333" s="4" t="inlineStr">
+      <c r="B335" s="4" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C333" s="4" t="n">
+      <c r="C335" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="D333" s="4" t="n">
+      <c r="D335" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="E333" s="4" t="n">
+      <c r="E335" s="4" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B334" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C334" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D334" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="E334" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B335" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C335" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D335" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="E335" s="2" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="336">
@@ -7956,17 +7956,17 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="337">
@@ -7977,17 +7977,17 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C337" s="2" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="338">
@@ -7998,59 +7998,59 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="inlineStr">
+      <c r="A339" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B339" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C339" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D339" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E339" s="3" t="n">
-        <v>0</v>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D339" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="3" t="inlineStr">
+      <c r="A340" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B340" s="3" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C340" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D340" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E340" s="3" t="n">
-        <v>0</v>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="D340" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="341">
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D341" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E341" s="3" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D342" s="3" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E342" s="3" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E344" s="3" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E345" s="3" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E346" s="3" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E347" s="3" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E348" s="3" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="D349" s="3" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="E349" s="3" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E350" s="3" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E351" s="3" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E352" s="3" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E353" s="3" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D354" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E356" s="3" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E357" s="3" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E358" s="3" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E359" s="3" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D360" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E360" s="3" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D361" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E361" s="3" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E362" s="3" t="n">
         <v>0</v>
@@ -8523,14 +8523,14 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D363" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E363" s="3" t="n">
         <v>0</v>
@@ -8539,19 +8539,19 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C364" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D364" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E364" s="3" t="n">
         <v>0</v>
@@ -8560,19 +8560,19 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C365" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D365" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E365" s="3" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C366" s="3" t="n">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D368" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E368" s="3" t="n">
         <v>0</v>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="3" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="3" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
@@ -8747,66 +8747,66 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="inlineStr">
-        <is>
-          <t>雷克萨斯</t>
-        </is>
-      </c>
-      <c r="B374" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C374" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="D374" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E374" s="2" t="n">
-        <v>-1</v>
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t>阿斯顿·马丁</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C374" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E374" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
+          <t>阿斯顿·马丁</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C375" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
           <t>雷克萨斯</t>
         </is>
       </c>
-      <c r="B375" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C375" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D375" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E375" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" s="3" t="inlineStr">
-        <is>
-          <t>雷克萨斯</t>
-        </is>
-      </c>
-      <c r="B376" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C376" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D376" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E376" s="3" t="n">
-        <v>0</v>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D376" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E376" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="377">
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C377" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E377" s="3" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E378" s="3" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E379" s="3" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E380" s="3" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E381" s="3" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E382" s="3" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E383" s="3" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E384" s="3" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E385" s="3" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E386" s="3" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C387" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E387" s="3" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="3" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="3" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="3" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="3" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="3" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="3" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="3" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="3" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="3" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="3" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="3" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="3" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="3" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="3" t="n">
         <v>0</v>
@@ -9363,59 +9363,59 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D403" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C403" s="3" t="n">
+      <c r="C405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D403" s="3" t="n">
+      <c r="D405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E403" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B404" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C404" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="D404" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="E404" s="2" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C405" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="D405" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E405" s="2" t="n">
-        <v>-1</v>
+      <c r="E405" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="407">
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D407" s="2" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E407" s="2" t="n">
         <v>-1</v>
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C408" s="2" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D408" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E408" s="2" t="n">
         <v>-1</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>-1</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>-1</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>-1</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>-1</v>
@@ -9573,59 +9573,59 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="3" t="inlineStr">
+      <c r="A414" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B414" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C414" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="D414" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="E414" s="3" t="n">
-        <v>0</v>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E414" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="3" t="inlineStr">
+      <c r="A415" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B415" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C415" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="D415" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="E415" s="3" t="n">
-        <v>0</v>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E415" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="416">
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E426" s="3" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E427" s="3" t="n">
         <v>0</v>
@@ -9888,59 +9888,59 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D428" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="E428" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C429" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D429" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E429" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C428" s="3" t="n">
+      <c r="C430" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D428" s="3" t="n">
+      <c r="D430" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E428" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B429" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C429" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="D429" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="E429" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B430" s="4" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C430" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="D430" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="E430" s="4" t="n">
-        <v>1</v>
+      <c r="E430" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>辽宁</t>
         </is>
       </c>
-      <c r="C434" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="D434" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="E434" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11001,7 +11043,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11016,7 +11058,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11070,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11043,7 +11085,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11955,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11928,7 +11970,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11982,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -11955,7 +11997,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12630,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12603,7 +12645,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12657,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12630,7 +12672,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
     </row>
@@ -14716,22 +14758,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14741,29 +14783,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14773,29 +14815,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14805,7 +14847,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
@@ -14849,17 +14891,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14869,7 +14911,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -14886,12 +14928,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14901,29 +14943,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14933,29 +14975,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -14965,29 +15007,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -14997,29 +15039,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15029,7 +15071,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
@@ -15041,17 +15083,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15061,29 +15103,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15093,29 +15135,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15125,29 +15167,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15157,29 +15199,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15189,29 +15231,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15221,29 +15263,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15253,29 +15295,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15285,7 +15327,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
@@ -15297,17 +15339,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15317,29 +15359,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15349,29 +15391,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15381,29 +15423,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15413,7 +15455,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15425,17 +15467,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15445,7 +15487,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15457,17 +15499,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15477,29 +15519,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15509,29 +15551,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15541,29 +15583,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15573,29 +15615,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15605,29 +15647,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15637,29 +15679,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15669,29 +15711,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15701,29 +15743,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15733,7 +15775,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15745,17 +15787,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15765,7 +15807,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15777,17 +15819,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15797,7 +15839,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
@@ -15809,17 +15851,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15829,7 +15871,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15841,17 +15883,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15861,29 +15903,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15893,7 +15935,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -15932,22 +15974,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15957,7 +15999,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -15969,17 +16011,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -15989,7 +16031,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16001,17 +16043,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16021,29 +16063,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16053,7 +16095,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16065,17 +16107,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16085,7 +16127,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16097,17 +16139,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16129,17 +16171,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16156,22 +16198,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16193,17 +16235,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16220,22 +16262,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16257,17 +16299,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16289,17 +16331,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16316,22 +16358,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16348,22 +16390,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16385,17 +16427,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16417,17 +16459,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16444,22 +16486,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16476,22 +16518,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16508,22 +16550,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16540,22 +16582,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16577,17 +16619,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16609,17 +16651,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16636,22 +16678,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16668,22 +16710,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16700,22 +16742,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16769,17 +16811,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16801,17 +16843,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16833,17 +16875,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16865,17 +16907,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16892,22 +16934,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16924,22 +16966,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16956,22 +16998,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -16988,22 +17030,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17020,22 +17062,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17057,17 +17099,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17084,22 +17126,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17121,17 +17163,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17148,22 +17190,22 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17185,17 +17227,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17217,17 +17259,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17308,22 +17350,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17333,7 +17375,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -17345,17 +17387,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -17365,7 +17407,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17377,17 +17419,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17397,7 +17439,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17409,17 +17451,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17429,29 +17471,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17461,7 +17503,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
     </row>
@@ -13089,7 +13089,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
     </row>
@@ -14758,22 +14758,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14783,29 +14783,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14815,29 +14815,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14847,29 +14847,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14879,29 +14879,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14911,29 +14911,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14943,29 +14943,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14975,29 +14975,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15007,29 +15007,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
@@ -15051,17 +15051,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15071,29 +15071,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15103,29 +15103,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15135,29 +15135,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
@@ -15179,17 +15179,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15199,29 +15199,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15231,29 +15231,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15263,29 +15263,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15295,29 +15295,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15339,17 +15339,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15359,29 +15359,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15391,29 +15391,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15435,17 +15435,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15455,29 +15455,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15487,29 +15487,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15519,29 +15519,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15551,29 +15551,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15583,29 +15583,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15627,17 +15627,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15659,17 +15659,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15691,17 +15691,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15711,29 +15711,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15743,29 +15743,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15787,17 +15787,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
@@ -15819,17 +15819,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15851,17 +15851,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15871,29 +15871,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15903,29 +15903,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
@@ -15974,22 +15974,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16011,17 +16011,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16043,17 +16043,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16075,17 +16075,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16095,29 +16095,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16144,12 +16144,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16171,17 +16171,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16203,17 +16203,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16230,22 +16230,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16262,22 +16262,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16299,17 +16299,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16331,17 +16331,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16358,22 +16358,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16390,22 +16390,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16427,17 +16427,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16459,17 +16459,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16491,17 +16491,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16518,22 +16518,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16550,22 +16550,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16582,22 +16582,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16614,22 +16614,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16646,22 +16646,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16683,17 +16683,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16715,17 +16715,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16742,22 +16742,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16806,22 +16806,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16838,22 +16838,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16875,17 +16875,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16902,22 +16902,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16939,17 +16939,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16971,17 +16971,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16998,22 +16998,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17030,22 +17030,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17062,22 +17062,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17099,17 +17099,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17131,17 +17131,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17158,22 +17158,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17195,17 +17195,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17227,17 +17227,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17259,17 +17259,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17286,22 +17286,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -17311,29 +17311,29 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -17343,29 +17343,29 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
@@ -17387,17 +17387,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -17407,29 +17407,29 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17451,17 +17451,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
     </row>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
     </row>
@@ -14758,22 +14758,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14783,29 +14783,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14815,29 +14815,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14847,29 +14847,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14879,29 +14879,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14911,29 +14911,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14943,29 +14943,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -14987,17 +14987,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15007,29 +15007,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15039,29 +15039,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15071,29 +15071,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15103,29 +15103,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15135,29 +15135,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15179,17 +15179,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15199,29 +15199,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15231,29 +15231,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15263,29 +15263,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
@@ -15339,17 +15339,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15359,29 +15359,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15391,29 +15391,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15423,29 +15423,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15455,29 +15455,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15487,29 +15487,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15519,29 +15519,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15551,29 +15551,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15583,29 +15583,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15615,29 +15615,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15647,29 +15647,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15679,29 +15679,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15711,29 +15711,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15743,29 +15743,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15787,17 +15787,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15819,17 +15819,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -15851,17 +15851,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15871,29 +15871,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15915,17 +15915,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15935,29 +15935,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -15979,17 +15979,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16011,17 +16011,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16043,17 +16043,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16063,14 +16063,14 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -16080,12 +16080,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16171,17 +16171,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16203,17 +16203,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16230,22 +16230,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16262,22 +16262,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16294,22 +16294,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16331,17 +16331,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16363,17 +16363,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16395,17 +16395,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16427,17 +16427,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16459,17 +16459,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16486,22 +16486,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16523,17 +16523,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16550,22 +16550,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16582,22 +16582,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16614,22 +16614,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16646,22 +16646,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16678,22 +16678,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16715,17 +16715,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16747,17 +16747,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16774,22 +16774,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16806,22 +16806,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16838,22 +16838,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16870,7 +16870,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -16880,12 +16880,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16902,22 +16902,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16939,17 +16939,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16971,17 +16971,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17003,17 +17003,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17035,17 +17035,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17067,17 +17067,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17094,22 +17094,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17158,22 +17158,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17195,17 +17195,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17227,17 +17227,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17286,22 +17286,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -17311,29 +17311,29 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -17343,29 +17343,29 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17414,22 +17414,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（123家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（122家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,14 +686,14 @@
         <v>827</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.0%</t>
         </is>
       </c>
     </row>
@@ -875,10 +875,10 @@
         <v>8714</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8636</v>
+        <v>8637</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-78</v>
+        <v>-77</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>-1</v>
@@ -5163,14 +5163,14 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>-1</v>
@@ -5184,38 +5184,38 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D205" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E205" s="2" t="n">
-        <v>-1</v>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -5226,14 +5226,14 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E206" s="3" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E208" s="3" t="n">
         <v>0</v>
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="E209" s="3" t="n">
         <v>0</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E210" s="3" t="n">
         <v>0</v>
@@ -5331,14 +5331,14 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E211" s="3" t="n">
         <v>0</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="E212" s="3" t="n">
         <v>0</v>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="E213" s="3" t="n">
         <v>0</v>
@@ -5394,14 +5394,14 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E214" s="3" t="n">
         <v>0</v>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10088,6 +10088,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10116,6 +10117,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -10143,6 +10149,11 @@
           <t>运城经济技术开发区二十二区机场路以南05号(锦华丰田隔壁)</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10170,6 +10181,11 @@
           <t>双街镇京津公路东侧双江道南庞大汽贸园内21号</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10197,6 +10213,11 @@
           <t>山西省大同市云州区经济技术开发区大同瑞湖新能源汽车服务城A区1号</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -10224,6 +10245,11 @@
           <t>贵州省毕节市金海湖新区双山小瓦路国际汽车城</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -10251,6 +10277,11 @@
           <t>辽宁省丹东市振兴区集环南路1号</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10278,6 +10309,11 @@
           <t>河南省濮阳市华龙区孟轲乡201街道001街坊德众汽车产业园（816-02）0005幢标准厂房5号</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -10305,6 +10341,11 @@
           <t>贵州省铜仁市万山区仁山街道汽车南站西侧唐家寨火焰垱村</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -10332,6 +10373,11 @@
           <t>吉林省松原市宁江区五环大街 3777 号B1层中庭</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -10359,6 +10405,11 @@
           <t>文忠街333号眉山东坡万达广场YX-HD-ZT-001</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -10386,6 +10437,11 @@
           <t>西中环路与双岭路交叉口南远东新能源汽车市场9号门</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -10413,6 +10469,11 @@
           <t>广东省东莞市塘厦镇莲湖社区塘厦大道中 38 号天虹购物中心</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -10440,6 +10501,11 @@
           <t>头屯河公路2345号新疆天恒基国际汽车文化城62栋</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10467,6 +10533,11 @@
           <t>江西省萍乡市安源区康庄路与萍安北大道交汇处萍乡天虹购物中心1F中庭</t>
         </is>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260525~20260525，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10494,6 +10565,11 @@
           <t>山东省淄博市张店区山泉路212号院内</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260511~20260608，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10521,6 +10597,11 @@
           <t>南京市栖霞区仙尧路27号 C2-1</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10548,6 +10629,11 @@
           <t>无锡市梁溪区广和路5-1号</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10575,6 +10661,11 @@
           <t>浙江省绍兴市上虞区曹娥街道五星东路8号上百万悦城1F楼136+147</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -10602,6 +10693,11 @@
           <t>仙桃市仙洪路21号</t>
         </is>
       </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10629,6 +10725,11 @@
           <t>陕西省西安市浐灞生态区欧亚一路1688号（原方程豹展厅）</t>
         </is>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -10656,6 +10757,11 @@
           <t>山东省济南市章丘区明水经济开发区创业路</t>
         </is>
       </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10683,6 +10789,11 @@
           <t>山东省滨州市经济技术开发区长江一路与渤海二十四路交叉口西北角505号</t>
         </is>
       </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -10710,6 +10821,11 @@
           <t>浙江省杭州市滨江区西兴街道江陵路1760号</t>
         </is>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10737,6 +10853,11 @@
           <t>湖北省武汉市洪山区和平乡铁机村2号A区东区03商铺</t>
         </is>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -10764,6 +10885,11 @@
           <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10791,6 +10917,11 @@
           <t>宁夏回族自治区银川市金凤区阅彩城一层101号商铺前</t>
         </is>
       </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -10818,6 +10949,11 @@
           <t>山东省济南市历下区经十路 1111号济南万象城LG2层 服务台旁</t>
         </is>
       </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -10845,6 +10981,11 @@
           <t>广东省佛山市顺德区大良广珠公路新松路段新协力汽车城第二营业部</t>
         </is>
       </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -10872,6 +11013,11 @@
           <t>新疆维吾尔自治区伊犁哈萨克自治州伊宁市山东路199号伊犁悦桐购物中心一楼X-1F-52</t>
         </is>
       </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -10899,6 +11045,11 @@
           <t>辽宁省大连市甘井子区山东路350号华南万象汇LG178铺</t>
         </is>
       </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -10926,6 +11077,11 @@
           <t>重庆市南岸区江南大道15号A馆-1F-31b/32</t>
         </is>
       </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -10953,6 +11109,11 @@
           <t>安徽省黄山市屯溪区屯光大道10号</t>
         </is>
       </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -10980,6 +11141,11 @@
           <t>浙江省宁波市宁海县平安西路26号理想汽车</t>
         </is>
       </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -11007,6 +11173,11 @@
           <t>沈阳市东陵路26号</t>
         </is>
       </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260518，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -11034,6 +11205,11 @@
           <t>内蒙古自治区呼和浩特市回民区锡林郭勒北路振华购物中心一层华为授权店</t>
         </is>
       </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -11043,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11058,7 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11085,7 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11115,6 +11301,11 @@
           <t>山西省晋城市城区上元街兰花城购物中心底2号商铺</t>
         </is>
       </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -11142,6 +11333,11 @@
           <t>广东省东莞市塘厦镇东深路塘厦段2号101室</t>
         </is>
       </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -11169,6 +11365,11 @@
           <t>广东省深圳市龙岗区园山街道保安社区红棉四路23号中联展·新能源汽车城3栋110</t>
         </is>
       </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -11196,6 +11397,11 @@
           <t>广东省潮州市潮安区潮汕公路与乌洋环乡路交界处</t>
         </is>
       </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260622，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -11223,6 +11429,11 @@
           <t>浙江省金华市金东区多湖街道李渔东路 300 号万达广场 1F 层 1005B,1006</t>
         </is>
       </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -11250,6 +11461,11 @@
           <t>湖北省武汉市硚口区工农路与惠安大道交汇处汉江湾C2地块</t>
         </is>
       </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -11277,6 +11493,11 @@
           <t>甘肃省天水市麦积区花牛镇花牛村3组155号</t>
         </is>
       </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260622，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -11304,6 +11525,11 @@
           <t>辽宁省沈阳市浑南区-远航中路33-2-号门</t>
         </is>
       </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -11329,6 +11555,11 @@
       <c r="E46" s="4" t="inlineStr">
         <is>
           <t>陕西省榆林市高新区长兴路175号榆林榆阳万达广场1F-2A（华为智能生活馆）</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11343,14 +11574,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11379,6 +11611,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -11406,6 +11643,11 @@
           <t>山东省济宁市高新区同济路7号</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -11433,6 +11675,11 @@
           <t>兴宁区金仑路34号</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -11460,6 +11707,11 @@
           <t>江苏省淮安市清江浦区飞耀路52号</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -11487,6 +11739,11 @@
           <t>闽侯县尚干镇良安路26号</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -11514,6 +11771,11 @@
           <t>昌平区北七家镇北京北辰亚运村汽车交易市场中心3-1、3-2</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -11541,6 +11803,11 @@
           <t>花都区迎春路15号</t>
         </is>
       </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -11568,6 +11835,11 @@
           <t>宿豫区洪泽湖路北侧张家港大道西侧50米</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -11595,6 +11867,11 @@
           <t>句容市长龙山路南侧与宁杭路西侧爵鼎综合商贸楼</t>
         </is>
       </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -11622,6 +11899,11 @@
           <t>衢江区振兴东路777-2号</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -11649,6 +11931,11 @@
           <t>伍家岗区东站路189号</t>
         </is>
       </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -11676,6 +11963,11 @@
           <t>七里河区西津西路1210号（甘肃仕通公司院内）</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -11703,6 +11995,11 @@
           <t>吉林省长春市绿园区基隆中街817号</t>
         </is>
       </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -11730,6 +12027,11 @@
           <t>安徽省合肥市庐阳区蒙城北路2100号,230000</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -11757,6 +12059,11 @@
           <t>东营市东营区西四路914号</t>
         </is>
       </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -11784,6 +12091,11 @@
           <t>广州市天河区博汇街1号</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -11811,6 +12123,11 @@
           <t>深圳市龙华区大浪街道浪口社区浪口工业园47号1层邮编:518110</t>
         </is>
       </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -11838,6 +12155,11 @@
           <t>浙江省嘉兴市经济技术开发区东方路1121号</t>
         </is>
       </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -11865,6 +12187,11 @@
           <t xml:space="preserve">浙江省温州市平阳县昆阳镇建丰村路口104国道边 </t>
         </is>
       </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -11892,6 +12219,11 @@
           <t>黄石市经济技术开发区金山大道189号B栋研发楼办公室</t>
         </is>
       </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -11919,6 +12251,11 @@
           <t>中环南路999号-5号一层-1 南湖区 314051</t>
         </is>
       </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -11946,6 +12283,11 @@
           <t>上海市金山区龙皓路1088号</t>
         </is>
       </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -11955,7 +12297,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -11970,7 +12312,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -11982,7 +12329,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -11997,7 +12344,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12027,6 +12379,11 @@
           <t>唐槐园区唐槐路98号1幢一层厂房</t>
         </is>
       </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -12054,6 +12411,11 @@
           <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -12081,6 +12443,11 @@
           <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -12108,6 +12475,11 @@
           <t>新华路6号</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -12135,6 +12507,11 @@
           <t>湖北省武汉市武昌区和平大道659号滨江天街一层5号门中庭</t>
         </is>
       </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 4 期</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -12162,6 +12539,11 @@
           <t>重庆汇集汽贸广场二期工程</t>
         </is>
       </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -12189,6 +12571,11 @@
           <t>上海市嘉定区阿克苏路1099号</t>
         </is>
       </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -12216,6 +12603,11 @@
           <t>北京市朝阳区北四环东路73号居然之家未来广场店一层</t>
         </is>
       </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -12243,6 +12635,11 @@
           <t>山西省太原市万柏林区迎泽西大街铁道西侧闫家沟铁西综合楼29号小鹏汽车</t>
         </is>
       </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -12270,6 +12667,11 @@
           <t>山西省忻州市忻州市忻府区七一北路汽贸园</t>
         </is>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -12279,22 +12681,27 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车昌吉市汽车城销售展厅</t>
+          <t>小鹏汽车南京江宁宝⻰销售展厅</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>昌吉回族自治州</t>
+          <t>南京市</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区昌吉市北五路智慧新能源汽车城</t>
+          <t>江苏省南京市江宁区麒麟街道丹霞路169号M1-L1-022/065</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12713,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车南京江宁宝⻰销售展厅</t>
+          <t>小鹏汽车无锡惠山万达销售展厅</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -12316,12 +12723,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>江苏省南京市江宁区麒麟街道丹霞路169号M1-L1-022/065</t>
+          <t>无锡市惠山区吴韵路321号1F1025，1026号铺</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12333,7 +12745,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡惠山万达销售展厅</t>
+          <t>小鹏汽车盐城中南城销售中心</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -12343,12 +12755,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>盐城市</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>无锡市惠山区吴韵路321号1F1025，1026号铺</t>
+          <t>江苏省盐城市盐都区解放南路278号大有境购物中心1楼1013号</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12777,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城中南城销售中心</t>
+          <t>小鹏汽车苏州狮山龙湖天街销售展厅</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -12370,12 +12787,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>盐城市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区解放南路278号大有境购物中心1楼1013号</t>
+          <t>江苏省苏州市高新区塔园路181号苏州狮山天街1层[SZSSTJ-A-1F-44]铺</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12387,22 +12809,27 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车苏州狮山龙湖天街销售展厅</t>
+          <t>小鹏汽车抚州万达广场销售中心</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>抚州市</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市高新区塔园路181号苏州狮山天街1层[SZSSTJ-A-1F-44]铺</t>
+          <t>江西省抚州市抚州高新技术产业开发区万达场室内步行街1F层A-A号</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12414,22 +12841,27 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州万达广场销售中心</t>
+          <t>小鹏汽车周口南环汽车城销售中心</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>抚州市</t>
+          <t>周口市</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>江西省抚州市抚州高新技术产业开发区万达场室内步行街1F层A-A号</t>
+          <t>河南省周口市川汇区众恒新能源汽车城院内</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12441,22 +12873,27 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环汽车城销售中心</t>
+          <t>小鹏汽车湖州长兴万达销售展厅</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>周口市</t>
+          <t>湖州市</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区众恒新能源汽车城院内</t>
+          <t>浙江省湖州市长兴县忻湖路长兴万达广场1号门</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12468,22 +12905,27 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车湖州长兴万达销售展厅</t>
+          <t>小鹏汽车海口王府井销售展厅</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>湖州市</t>
+          <t>海口市</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>浙江省湖州市长兴县忻湖路长兴万达广场1号门</t>
+          <t>龙华区海秀中路71号王府井海垦广场1F层L1-67号</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12495,22 +12937,27 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车海口王府井销售展厅</t>
+          <t>小鹏汽车武汉经开永旺销售中心</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>海口市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>龙华区海秀中路71号王府井海垦广场1F层L1-67号</t>
+          <t>湖北省武汉市经济开发区江城大道408号永旺梦乐城B馆1号门</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12522,49 +12969,59 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉经开永旺销售中心</t>
+          <t>小鹏汽车咸阳沣西吾悦销售展厅</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>咸阳市</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市经济开发区江城大道408号永旺梦乐城B馆1号门</t>
+          <t>陕西省咸阳市秦都区统一西路643号沣西吾悦广场1017铺</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳沣西吾悦销售展厅</t>
+          <t>上海世博源新能源空间</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>咸阳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦都区统一西路643号沣西吾悦广场1017铺</t>
+          <t>上海市浦东新区上南路168号世博源4区</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12576,22 +13033,27 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>上海世博源新能源空间</t>
+          <t>广元万达广场新能源空间</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广元市</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区上南路168号世博源4区</t>
+          <t>四川省广元市利州区万缘街道万源万达广场1楼中庭</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12603,7 +13065,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>广元万达广场新能源空间</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12613,12 +13075,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>广元市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>四川省广元市利州区万缘街道万源万达广场1楼中庭</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12630,7 +13097,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -12645,7 +13112,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12657,22 +13129,27 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>威海威高购物广场新能源空间</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>威海市</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>威海市环翠区新威路27号</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12684,7 +13161,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>威海威高购物广场新能源空间</t>
+          <t>泰安吾悦广场泰山店新能源空间</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -12694,12 +13171,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>威海市</t>
+          <t>泰安市</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>威海市环翠区新威路27号</t>
+          <t>泰安市泰山区天烛号峰路39三5号</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12711,7 +13193,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>泰安吾悦广场泰山店新能源空间</t>
+          <t>烟台大悦城新能源空间</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -12721,12 +13203,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>泰安市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>泰安市泰山区天烛号峰路39三5号</t>
+          <t>烟台市芝罘区北马路155号</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12738,7 +13225,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>烟台大悦城新能源空间</t>
+          <t>青岛伟东乐客城新能源空间</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -12748,12 +13235,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>青岛市</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>烟台市芝罘区北马路155号</t>
+          <t>山东省青岛市李沧区夏庄路7号乐客城负一层</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -12765,22 +13257,27 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>青岛伟东乐客城新能源空间</t>
+          <t>中山德顺行小榄卫星店</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>中山市</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路7号乐客城负一层</t>
+          <t>广东省中山市小榄镇永宁社区菊城大道西131号之三</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12792,7 +13289,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>中山德顺行小榄卫星店</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -12802,12 +13299,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>中山市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省中山市小榄镇永宁社区菊城大道西131号之三</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12819,7 +13321,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -12834,7 +13336,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12846,7 +13353,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -12861,7 +13368,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12873,7 +13385,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -12883,12 +13395,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12918,6 +13435,11 @@
           <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -12945,6 +13467,11 @@
           <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -12954,22 +13481,27 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>南京金茂览秀城新能源空间</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>南京市</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>江苏省南京市鼓楼区中央路201号</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12981,7 +13513,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>南京金茂览秀城新能源空间</t>
+          <t>常州飞龙吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -12991,12 +13523,17 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>常州市</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>江苏省南京市鼓楼区中央路201号</t>
+          <t>江苏省常州市新北区飞龙中路166号</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13545,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>常州飞龙吾悦广场新能源空间</t>
+          <t>扬州京华城新能源空间</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -13018,12 +13555,17 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>常州市</t>
+          <t>扬州市</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙中路166号</t>
+          <t>江苏省扬州市邗江区京华城路168号</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13577,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>扬州京华城新能源空间</t>
+          <t>无锡茂业天地（清扬店）新能源空间</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -13045,12 +13587,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>扬州市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省扬州市邗江区京华城路168号</t>
+          <t>江苏省无锡市梁溪区清扬路128号</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13609,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>无锡茂业天地（清扬店）新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13072,12 +13619,17 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省无锡市梁溪区清扬路128号</t>
+          <t>苏州市昆山市青阳北路234号</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13089,7 +13641,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13104,7 +13656,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -13116,22 +13673,27 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>南昌绿地名沃维修中心</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>江西省南昌市经济技术开发区玉屏东大街551号</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13705,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>南昌绿地名沃维修中心</t>
+          <t>赣州兴国翡翠广场新能源空间</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -13153,12 +13715,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>南昌市</t>
+          <t>赣州市</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>江西省南昌市经济技术开发区玉屏东大街551号</t>
+          <t>江西省赣州市兴国县兴国大道477号（兴国世茂翡翠城内）</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
         </is>
       </c>
     </row>
@@ -13170,22 +13737,27 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>赣州兴国翡翠广场新能源空间</t>
+          <t>邢台清河北国商城新能源空间</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>赣州市</t>
+          <t>邢台市</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>江西省赣州市兴国县兴国大道477号（兴国世茂翡翠城内）</t>
+          <t>邢台市清河县珠江街与天山中路交叉口西南240米</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13197,22 +13769,27 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>邢台清河北国商城新能源空间</t>
+          <t>台州中国日用品商城新能源空间</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>邢台市</t>
+          <t>台州市</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>邢台市清河县珠江街与天山中路交叉口西南240米</t>
+          <t>浙江省台州市路桥区浙江省台州市路桥财富大道999号</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13224,22 +13801,27 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>台州中国日用品商城新能源空间</t>
+          <t>长沙步步高星城天地新能源空间</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>台州市</t>
+          <t>长沙市</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区浙江省台州市路桥财富大道999号</t>
+          <t>长沙市雨花区湘府东路二段95步步高·星城天地</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13251,22 +13833,27 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>长沙步步高星城天地新能源空间</t>
+          <t>兰州中心新能源空间</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>兰州市</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>长沙市雨花区湘府东路二段95步步高·星城天地</t>
+          <t>甘肃省兰州市七里河区甘肃省兰州市七里河区建兰路街道西津西路16号</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13278,22 +13865,27 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>兰州中心新能源空间</t>
+          <t>泉州晋江百捷上悦城新能源空间</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>兰州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>甘肃省兰州市七里河区甘肃省兰州市七里河区建兰路街道西津西路16号</t>
+          <t>福建省泉州市晋江市涌泉路与望江路交汇处北侧</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13305,22 +13897,27 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>泉州晋江百捷上悦城新能源空间</t>
+          <t>沈阳中街吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>沈阳市</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>福建省泉州市晋江市涌泉路与望江路交汇处北侧</t>
+          <t>辽宁省沈阳市大东区津桥路7号沈阳中街</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13332,22 +13929,27 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沈阳中街吾悦广场新能源空间</t>
+          <t>重庆宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>沈阳市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>辽宁省沈阳市大东区津桥路7号沈阳中街</t>
+          <t>重庆市两江新区汇流路2号</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13359,22 +13961,27 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>重庆宜家家居新能源空间</t>
+          <t>延安吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>延安市</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>重庆市两江新区汇流路2号</t>
+          <t>延安市宝塔区新城街道轩辕大道与子长路交汇处</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13386,49 +13993,59 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>延安吾悦广场新能源空间</t>
+          <t>大庆星耀天地新能源空间</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>延安市</t>
+          <t>大庆市</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>延安市宝塔区新城街道轩辕大道与子长路交汇处</t>
+          <t>黑龙江省大庆市龙凤区世纪大道与龙永路交叉口</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>大庆星耀天地新能源空间</t>
+          <t>北京清河万象汇体验店</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>大庆市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省大庆市龙凤区世纪大道与龙永路交叉口</t>
+          <t>北京市海淀区清河中街68号</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13440,22 +14057,27 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>北京清河万象汇体验店</t>
+          <t>成都悠方购物中心体验店</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>北京市海淀区清河中街68号</t>
+          <t>四川省成都市武侯区交子大道300号</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13467,22 +14089,27 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心体验店</t>
+          <t>珠海高新宝龙广场体验店</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>珠海市</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区交子大道300号</t>
+          <t>广东省珠海市高新区唐家湾镇金峰北路88号宝龙广场一层M1-L1-009</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13494,22 +14121,27 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>珠海高新宝龙广场体验店</t>
+          <t>赣州万象城</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>珠海市</t>
+          <t>赣州市</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>广东省珠海市高新区唐家湾镇金峰北路88号宝龙广场一层M1-L1-009</t>
+          <t>江西省赣州市章贡区章江新区新赣州大道8 号赣州万象城1层AVSPAL111 点位</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13521,22 +14153,27 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>赣州万象城</t>
+          <t>邯郸美乐城</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>赣州市</t>
+          <t>邯郸市</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>江西省赣州市章贡区章江新区新赣州大道8 号赣州万象城1层AVSPAL111 点位</t>
+          <t>河北省邯郸市丛台区人民东路456号邯郸美乐城1层</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13548,22 +14185,27 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>邯郸美乐城</t>
+          <t>杭州余杭万达广场</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>邯郸市</t>
+          <t>杭州市</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>河北省邯郸市丛台区人民东路456号邯郸美乐城1层</t>
+          <t>浙江省杭州市余杭区文一西路1888号</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13575,49 +14217,59 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>杭州余杭万达广场</t>
+          <t>重庆龙湖江岸天街</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市余杭区文一西路1888号</t>
+          <t>重庆市南岸区江南大道15号A馆-LG1-CN-TD-04</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>重庆龙湖江岸天街</t>
+          <t>理想汽车北京龙湖房山熙悦天街零售中心</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>重庆市南岸区江南大道15号A馆-LG1-CN-TD-04</t>
+          <t>北京市房山区良乡东路龙湖房山熙悦天街购物中心A区3号门旁</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13629,22 +14281,27 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>理想汽车北京龙湖房山熙悦天街零售中心</t>
+          <t>理想汽车长春欧亚卖场零售中心</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>长春市</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>北京市房山区良乡东路龙湖房山熙悦天街购物中心A区3号门旁</t>
+          <t>吉林省长春市朝阳区飞跃路欧亚卖场10号门</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13656,22 +14313,27 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>理想汽车长春欧亚卖场零售中心</t>
+          <t>理想汽车芜湖八佰伴零售中心</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>长春市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>吉林省长春市朝阳区飞跃路欧亚卖场10号门</t>
+          <t>安徽省芜湖市中山北路33号芜湖八佰伴6023L1003-06铺位理想汽车</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13683,22 +14345,27 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>理想汽车芜湖八佰伴零售中心</t>
+          <t>理想汽车济南世纪大道万达零售展厅</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>安徽省芜湖市中山北路33号芜湖八佰伴6023L1003-06铺位理想汽车</t>
+          <t>山东省济南市历城区世纪大道万达LG层1011</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13710,7 +14377,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>理想汽车济南世纪大道万达零售展厅</t>
+          <t>理想汽车烟台万达零售中心</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -13720,12 +14387,17 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市历城区世纪大道万达LG层1011</t>
+          <t>山东省烟台市芝罘区西关南街6号【1F】层【1002】号</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13737,22 +14409,27 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>理想汽车烟台万达零售中心</t>
+          <t>理想汽车张家港金茂览秀城零售展厅</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街6号【1F】层【1002】号</t>
+          <t>江苏省苏州市张家港市杨舍镇戴巷路288号金茂览秀城1楼理想汽车</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13764,22 +14441,27 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>理想汽车张家港金茂览秀城零售展厅</t>
+          <t>理想汽车九江招商花园城零售中心</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>九江市</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇戴巷路288号金茂览秀城1楼理想汽车</t>
+          <t>江西省九江市八里湖新区九江招商花园城L111商铺</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13791,7 +14473,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>理想汽车九江招商花园城零售中心</t>
+          <t>理想汽车南昌红谷滩万达广场零售展厅</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13801,12 +14483,17 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>九江市</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>江西省九江市八里湖新区九江招商花园城L111商铺</t>
+          <t>江西省南昌市红谷滩万达广场一楼1002A商铺理想汽车</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13818,22 +14505,27 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>理想汽车南昌红谷滩万达广场零售展厅</t>
+          <t>理想汽车承德双滦服务中心（狮子园路临时店）</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>南昌市</t>
+          <t>承德市</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩万达广场一楼1002A商铺理想汽车</t>
+          <t>承德市双滦区狮子园路15号</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13845,22 +14537,27 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>理想汽车承德双滦服务中心（狮子园路临时店）</t>
+          <t>理想汽车洛阳大卫天地零售中心</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>承德市</t>
+          <t>洛阳市</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>承德市双滦区狮子园路15号</t>
+          <t>河南省洛阳市西工区解放路 的丹尼斯 【大卫天地】项目第【8】层 【22】号</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13872,22 +14569,27 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>理想汽车洛阳大卫天地零售中心</t>
+          <t>理想汽车铜仁万山服务中心（万山临时店）</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>洛阳市</t>
+          <t>铜仁市</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>河南省洛阳市西工区解放路 的丹尼斯 【大卫天地】项目第【8】层 【22】号</t>
+          <t>贵州省铜仁市万山区丹都街道桂花大道汽车城理想汽车服务中心001号</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13899,22 +14601,27 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山服务中心（万山临时店）</t>
+          <t>理想汽车锦州太和服务中心（锦港大街店）</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>铜仁市</t>
+          <t>锦州市</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>贵州省铜仁市万山区丹都街道桂花大道汽车城理想汽车服务中心001号</t>
+          <t>锦州市太和区锦港大街二段4号</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13926,22 +14633,27 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和服务中心（锦港大街店）</t>
+          <t>理想汽车宝鸡银泰城零售中心</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>锦州市</t>
+          <t>宝鸡市</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>锦州市太和区锦港大街二段4号</t>
+          <t>陕西省宝鸡市金台区金台大道66号商业广场【1F】层【1F-34-6、1F-34-7】号</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13953,49 +14665,59 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>理想汽车宝鸡银泰城零售中心</t>
+          <t>理想汽车哈尔滨道外服务中心（先锋路店）</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>宝鸡市</t>
+          <t>哈尔滨市</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市金台区金台大道66号商业广场【1F】层【1F-34-6、1F-34-7】号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路24-2号</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>理想汽车哈尔滨道外服务中心（先锋路店）</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>哈尔滨市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路24-2号</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14729,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14022,7 +14744,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14034,22 +14761,27 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 北京国瑞城</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>北京市东城区崇文门外大街18号</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14061,22 +14793,27 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 北京国瑞城</t>
+          <t>蔚来空间 | 长治万达广场</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>长治市</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>北京市东城区崇文门外大街18号</t>
+          <t>山西省长治市北二环路以南万达广场</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14088,22 +14825,27 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 长治万达广场</t>
+          <t>蔚来体验中心 | 东莞寮步</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>长治市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>山西省长治市北二环路以南万达广场</t>
+          <t>东莞市寮步镇寮步国际汽车城香市路10号</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14115,22 +14857,27 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东莞寮步</t>
+          <t>蔚来空间 | 余姚五彩城</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>东莞市</t>
+          <t>宁波市</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>东莞市寮步镇寮步国际汽车城香市路10号</t>
+          <t>浙江省宁波市余姚市城区城东路888号（余姚五彩城）L101A号商铺</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14889,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 余姚五彩城</t>
+          <t>蔚来空间 | 温州吾悦广场</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -14152,66 +14899,81 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市余姚市城区城东路888号（余姚五彩城）L101A号商铺</t>
+          <t>浙江省温州市龙湾区蒲州街道上江路150号温州吾悦广场1029商铺</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 温州吾悦广场</t>
+          <t>深圳大昌行坪珑</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区蒲州街道上江路150号温州吾悦广场1029商铺</t>
+          <t>深圳市坪山区坑梓街道开沃大厦首层</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>深圳大昌行坪珑</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>深圳市坪山区坑梓街道开沃大厦首层</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14223,22 +14985,27 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>华为智能生活馆•北京海淀大悦城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>北京市海淀区海淀大悦城一层1F-52、二层2F-48号商铺</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14250,22 +15017,27 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京海淀大悦城</t>
+          <t>华为智能生活馆•天津滨海吾悦</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>北京市海淀区海淀大悦城一层1F-52、二层2F-48号商铺</t>
+          <t>天津市滨海新区塘沽海洋科技园云山道819号滨海吾悦广场1层104</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -14277,22 +15049,27 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•天津滨海吾悦</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>天津市滨海新区塘沽海洋科技园云山道819号滨海吾悦广场1层104</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14304,22 +15081,27 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14331,22 +15113,27 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14358,7 +15145,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•阳江金山路</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -14368,12 +15155,17 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>阳江市</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>广东省阳江市江城区城北街道金山路432号</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14385,22 +15177,27 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•阳江金山路</t>
+          <t>华为授权体验店（金城中心）</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>阳江市</t>
+          <t>玉林市</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>广东省阳江市江城区城北街道金山路432号</t>
+          <t>广西壮族自治区玉林市人民东路802号金城中心B馆一层华为授权体验店</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14412,22 +15209,27 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（金城中心）</t>
+          <t>华为授权体验店（通州万达）</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>玉林市</t>
+          <t>南通市</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市人民东路802号金城中心B馆一层华为授权体验店</t>
+          <t>江苏省南通市通州区金沙镇万达广场一楼1030-1032 -1033B</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14439,7 +15241,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（通州万达）</t>
+          <t>鸿蒙智行尚界用户中心•苏州太阳路</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -14449,12 +15251,17 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>南通市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>江苏省南通市通州区金沙镇万达广场一楼1030-1032 -1033B</t>
+          <t>江苏省苏州市相城区元和街道太阳路2988-2号</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14466,7 +15273,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•苏州太阳路</t>
+          <t>华为智能生活馆•镇江丹阳金鹰</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -14476,12 +15283,17 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>镇江市</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区元和街道太阳路2988-2号</t>
+          <t>江苏省镇江市丹阳市金鹰国际购物中心1层室外停车场旁</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14493,22 +15305,27 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•镇江丹阳金鹰</t>
+          <t>华为智能生活馆•平顶山万达</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>镇江市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>江苏省镇江市丹阳市金鹰国际购物中心1层室外停车场旁</t>
+          <t>河南省平顶山市卫东区建设路899号平顶山万达广场1楼1010AB、1011A、1011B、1012</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14520,22 +15337,27 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•平顶山万达</t>
+          <t>鸿蒙智行授权用户中心•杭州梦马汽车小镇</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>杭州市</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>河南省平顶山市卫东区建设路899号平顶山万达广场1楼1010AB、1011A、1011B、1012</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼一层03号</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14547,22 +15369,27 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•杭州梦马汽车小镇</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>邵阳市</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼一层03号</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14574,22 +15401,27 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>华为授权体验店（海沧SM广场）</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>邵阳市</t>
+          <t>厦门市</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
+          <t>厦门市海沧区孚莲路1818号SM广场1F140-141铺位</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14601,22 +15433,27 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（海沧SM广场）</t>
+          <t>鸿蒙智行授权用户中心•六盘水钟山</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>厦门市</t>
+          <t>六盘水市</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>厦门市海沧区孚莲路1818号SM广场1F140-141铺位</t>
+          <t>贵州省六盘水市钟山区钟山西路白鹤高架桥北侧汽车文化广场（临时营业）</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14628,22 +15465,27 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•六盘水钟山</t>
+          <t>华为授权体验店（吾悦广场）</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>六盘水市</t>
+          <t>咸阳市</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>贵州省六盘水市钟山区钟山西路白鹤高架桥北侧汽车文化广场（临时营业）</t>
+          <t>陕西省咸阳市秦都区钓台街道沣西吾悦广场2楼华为</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14655,7 +15497,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（吾悦广场）</t>
+          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -14665,39 +15507,17 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>咸阳市</t>
+          <t>汉中市</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦都区钓台街道沣西吾悦广场2楼华为</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>汉中市</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
           <t>陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14758,22 +15578,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -14783,29 +15603,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -14815,29 +15635,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -14847,7 +15667,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -14859,17 +15679,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -14879,29 +15699,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -14911,7 +15731,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
@@ -14923,17 +15743,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -14943,7 +15763,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
@@ -14955,17 +15775,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -14975,29 +15795,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15007,29 +15827,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15039,29 +15859,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15071,7 +15891,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15083,17 +15903,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15103,29 +15923,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15135,29 +15955,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15167,29 +15987,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15199,7 +16019,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
@@ -15211,17 +16031,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15231,29 +16051,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15263,7 +16083,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
@@ -15275,17 +16095,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15295,29 +16115,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15327,29 +16147,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15359,29 +16179,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15391,29 +16211,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15423,29 +16243,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15455,29 +16275,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15487,29 +16307,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15519,29 +16339,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15551,29 +16371,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15583,29 +16403,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -15615,29 +16435,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -15647,7 +16467,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15659,17 +16479,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -15679,29 +16499,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -15711,7 +16531,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15723,17 +16543,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -15743,29 +16563,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -15775,29 +16595,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -15807,7 +16627,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15819,17 +16639,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -15839,29 +16659,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -15871,7 +16691,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
@@ -15883,17 +16703,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -15903,29 +16723,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -15935,7 +16755,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15974,7 +16794,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -15984,12 +16804,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -15999,7 +16819,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16043,17 +16863,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16063,29 +16883,29 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16095,29 +16915,29 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16127,7 +16947,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16139,17 +16959,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16171,17 +16991,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16198,22 +17018,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16230,22 +17050,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16262,22 +17082,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16294,22 +17114,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16331,17 +17151,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16358,22 +17178,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16395,17 +17215,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16422,22 +17242,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16459,17 +17279,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16491,17 +17311,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16523,17 +17343,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16555,17 +17375,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16587,17 +17407,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -16614,22 +17434,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -16646,22 +17466,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -16678,22 +17498,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -16710,7 +17530,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -16720,12 +17540,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -16742,22 +17562,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -16774,22 +17594,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -16806,22 +17626,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -16843,17 +17663,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -16870,7 +17690,7 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -16880,12 +17700,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -16907,17 +17727,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -16934,22 +17754,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -16971,17 +17791,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17003,17 +17823,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17030,22 +17850,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17067,17 +17887,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17094,22 +17914,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17126,22 +17946,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17163,17 +17983,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -17195,17 +18015,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -17227,17 +18047,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -17259,17 +18079,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -17286,22 +18106,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -17311,29 +18131,29 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -17343,29 +18163,29 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -17375,7 +18195,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
@@ -17414,22 +18234,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -17439,29 +18259,29 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -17471,29 +18291,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -17503,7 +18323,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11582,7 +11582,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「宁波兴宁保时捷中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「海宁保时捷认可易手车及售后服务中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「北京之星汽车服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「广州鸿粤嘉丰汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「镇江鹏龙星徽汽车销售服务有限公司句容分公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「衢州欧龙汽车有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「合肥恒信巨星汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「长沙宝创汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「蚌埠宝利丰汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「东营广宝汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「惠州市合宝汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「昆山中悦骏宝行汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「揭阳宝泰行汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「黄石喜之宝汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车山西省太原市小店区零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车重庆市两江新区西南汽贸城零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小鹏汽车常州金坛汽车城销售展厅」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小鹏汽车九江万达广场销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小鹏汽车新乡南环汽车城销售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13304,12 +13304,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「理想汽车哈尔滨道外授权钣喷中心（先锋路店）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（金鹰中心）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（万达茂）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「鸿蒙智行授权用户中心•苏州太阳路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「鸿蒙智行授权用户中心•汉中兴汉路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -15578,22 +15578,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
         </is>
       </c>
     </row>
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•玉林人民东路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•西安北辰大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15795,14 +15795,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15859,14 +15859,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -15876,12 +15876,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>华为智能生活馆•成都锦华万达</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
         </is>
       </c>
     </row>
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16019,14 +16019,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -16115,29 +16115,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -16243,29 +16243,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -16275,29 +16275,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -16307,29 +16307,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -16339,29 +16339,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -16371,29 +16371,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -16403,29 +16403,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16435,29 +16435,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16467,29 +16467,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16499,29 +16499,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
         </is>
       </c>
     </row>
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16595,29 +16595,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -16666,22 +16666,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16691,29 +16691,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16723,29 +16723,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16787,29 +16787,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16851,14 +16851,14 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -17375,17 +17375,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17466,22 +17466,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17530,7 +17530,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17594,22 +17594,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17626,7 +17626,7 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -17636,12 +17636,12 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17663,17 +17663,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17722,22 +17722,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17754,22 +17754,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17786,22 +17786,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17914,22 +17914,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17978,22 +17978,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -18047,17 +18047,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -18106,22 +18106,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -18131,29 +18131,29 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -18163,29 +18163,29 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -18195,29 +18195,29 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -18227,29 +18227,29 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -18291,29 +18291,29 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>鸿蒙智行授权用户中心•长春净月</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（45家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（122家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（86条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（42家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（112家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（75条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,23 +845,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>1721</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>1715</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
+      <c r="B18" s="4" t="n">
+        <v>1452</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1453</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8714</v>
+        <v>8445</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8637</v>
+        <v>8375</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-77</v>
+        <v>-70</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
     </row>
@@ -9430,13 +9430,13 @@
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="407">
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D407" s="2" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E407" s="2" t="n">
         <v>-1</v>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="C408" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D408" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E408" s="2" t="n">
         <v>-1</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>-1</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>-1</v>
@@ -9531,101 +9531,101 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="inlineStr">
+      <c r="A412" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B412" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C412" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="D412" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="E412" s="2" t="n">
-        <v>-1</v>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C412" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D412" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E412" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="inlineStr">
+      <c r="A413" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B413" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C413" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="D413" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="E413" s="2" t="n">
-        <v>-1</v>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C413" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D413" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E413" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="inlineStr">
+      <c r="A414" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B414" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C414" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D414" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="E414" s="2" t="n">
-        <v>-1</v>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="C414" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D414" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E414" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="inlineStr">
+      <c r="A415" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B415" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C415" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D415" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="E415" s="2" t="n">
-        <v>-1</v>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C415" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D415" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E415" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="416">
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E426" s="3" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E427" s="3" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="E428" s="3" t="n">
         <v>0</v>
@@ -9909,38 +9909,38 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C429" s="3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E429" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="3" t="inlineStr">
+      <c r="A430" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B430" s="3" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C430" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D430" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E430" s="3" t="n">
-        <v>0</v>
+      <c r="B430" s="4" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C430" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D430" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E430" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>207</v>
+        <v>140</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="C434" s="4" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D434" s="4" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E434" s="4" t="n">
         <v>1</v>
@@ -10035,14 +10035,14 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C435" s="4" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E435" s="4" t="n">
         <v>1</v>
@@ -10056,17 +10056,17 @@
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C436" s="4" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D436" s="4" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•东莞塘厦林村汽车城</t>
+          <t>鸿蒙智行授权用户中心•深圳红棉四路</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>东莞市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>广东省东莞市塘厦镇东深路塘厦段2号101室</t>
+          <t>广东省深圳市龙岗区园山街道保安社区红棉四路23号中联展·新能源汽车城3栋110</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -11347,27 +11347,27 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳红棉四路</t>
+          <t>华为智能生活馆•金华金东万达</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>金华市</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区园山街道保安社区红棉四路23号中联展·新能源汽车城3栋110</t>
+          <t>浙江省金华市金东区多湖街道李渔东路 300 号万达广场 1F 层 1005B,1006</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11379,27 +11379,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•潮州潮汕公路</t>
+          <t>鸿蒙智行授权用户中心•武汉硚口新能源汽车园</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>潮州市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>广东省潮州市潮安区潮汕公路与乌洋环乡路交界处</t>
+          <t>湖北省武汉市硚口区工农路与惠安大道交汇处汉江湾C2地块</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11411,27 +11411,27 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•金华金东万达</t>
+          <t>鸿蒙智行授权用户中心•沈阳金廊</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>金华市</t>
+          <t>沈阳市</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>浙江省金华市金东区多湖街道李渔东路 300 号万达广场 1F 层 1005B,1006</t>
+          <t>辽宁省沈阳市浑南区-远航中路33-2-号门</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11443,121 +11443,25 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•武汉硚口新能源汽车园</t>
+          <t>华为智能生活馆•榆林万达广场</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>武汉市</t>
+          <t>榆林市</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区工农路与惠安大道交汇处汉江湾C2地块</t>
+          <t>陕西省榆林市高新区长兴路175号榆林榆阳万达广场1F-2A（华为智能生活馆）</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•天水华世汽车城</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>天水市</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>甘肃省天水市麦积区花牛镇花牛村3组155号</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260622，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•沈阳金廊</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>沈阳市</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>辽宁省沈阳市浑南区-远航中路33-2-号门</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•榆林万达广场</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>榆林市</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>陕西省榆林市高新区长兴路175号榆林榆阳万达广场1F-2A（华为智能生活馆）</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
@@ -11574,13 +11478,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
@@ -12297,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12312,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12329,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12344,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -13289,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13304,7 +13208,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13321,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13336,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13368,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13400,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13449,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13464,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -14953,27 +14857,27 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>华为智能生活馆•北京海淀大悦城</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>北京市海淀区海淀大悦城一层1F-52、二层2F-48号商铺</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14985,27 +14889,27 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京海淀大悦城</t>
+          <t>华为智能生活馆•天津滨海吾悦</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>北京市海淀区海淀大悦城一层1F-52、二层2F-48号商铺</t>
+          <t>天津市滨海新区塘沽海洋科技园云山道819号滨海吾悦广场1层104</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 8 期</t>
         </is>
       </c>
     </row>
@@ -15017,27 +14921,27 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•天津滨海吾悦</t>
+          <t>华为授权体验店（金城中心）</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>玉林市</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>天津市滨海新区塘沽海洋科技园云山道819号滨海吾悦广场1层104</t>
+          <t>广西壮族自治区玉林市人民东路802号金城中心B馆一层华为授权体验店</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>连续在档 8 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（金鹰中心）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -15049,27 +14953,27 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>华为授权体验店（通州万达）</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>南通市</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>江苏省南通市通州区金沙镇万达广场一楼1030-1032 -1033B</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（万达茂）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -15081,27 +14985,27 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>华为智能生活馆•镇江丹阳金鹰</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>镇江市</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>江苏省镇江市丹阳市金鹰国际购物中心1层室外停车场旁</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -15113,27 +15017,27 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为智能生活馆•平顶山万达</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>河南省平顶山市卫东区建设路899号平顶山万达广场1楼1010AB、1011A、1011B、1012</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -15145,27 +15049,27 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•阳江金山路</t>
+          <t>华为授权体验店（海沧SM广场）</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>阳江市</t>
+          <t>厦门市</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>广东省阳江市江城区城北街道金山路432号</t>
+          <t>厦门市海沧区孚莲路1818号SM广场1F140-141铺位</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -15177,347 +15081,27 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（金城中心）</t>
+          <t>华为授权体验店（吾悦广场）</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>玉林市</t>
+          <t>咸阳市</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市人民东路802号金城中心B馆一层华为授权体验店</t>
+          <t>陕西省咸阳市秦都区钓台街道沣西吾悦广场2楼华为</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（金鹰中心）」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（通州万达）</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>南通市</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>江苏省南通市通州区金沙镇万达广场一楼1030-1032 -1033B</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期；本期存在高相似店名「华为授权体验店（万达茂）」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•苏州太阳路</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>苏州市</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>江苏省苏州市相城区元和街道太阳路2988-2号</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期；本期存在高相似店名「鸿蒙智行授权用户中心•苏州太阳路」（疑似改名/合并，非真实关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•镇江丹阳金鹰</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>镇江市</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>江苏省镇江市丹阳市金鹰国际购物中心1层室外停车场旁</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•平顶山万达</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>平顶山市</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>河南省平顶山市卫东区建设路899号平顶山万达广场1楼1010AB、1011A、1011B、1012</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•杭州梦马汽车小镇</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号3号楼一层03号</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
           <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>邵阳市</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（海沧SM广场）</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>厦门市</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>厦门市海沧区孚莲路1818号SM广场1F140-141铺位</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•六盘水钟山</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>六盘水市</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>贵州省六盘水市钟山区钟山西路白鹤高架桥北侧汽车文化广场（临时营业）</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（吾悦广场）</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>咸阳市</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>陕西省咸阳市秦都区钓台街道沣西吾悦广场2楼华为</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•汉中兴汉路</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>汉中市</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>陕西省汉中市汉台区兴汉路七里车管所向东300米</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 9 期；本期存在高相似店名「鸿蒙智行授权用户中心•汉中兴汉路」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -15532,7 +15116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15578,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•呼伦贝尔大鹏汽车园</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15603,7 +15187,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201（临时营业） → 内蒙古自治区呼伦贝尔市鄂温克族自治旗巴彦托海镇物流园区呼伦贝尔市大鹏誉达汽车贸易有限公司4S店B座201</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15615,17 +15199,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15635,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•玉林人民东路</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15667,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区玉林市玉州区人民东路南侧国防大厦斜对面 → 广西壮族自治区玉林市玉州区名山街道人民东路中国石化玉林第九加油站对面</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15699,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•西安北辰大道</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15731,7 +15315,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市浐灞生态区北辰大道以东欧亚三路以南 → 陕西省西安市未央区北辰大道与欧亚三路东南角</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15743,17 +15327,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15763,14 +15347,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -15780,12 +15364,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15795,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15827,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15839,17 +15423,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15859,29 +15443,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•成都锦华万达</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15891,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市锦江区锦华路一段68号1幢1F层1011-1/1011-2号 → 四川省成都市锦江区锦华路一段68号1栋一层1011</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15923,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15955,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•太原诺维兰汽车公园</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15987,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山西省太原市转型综合改革示范区唐槐产业园大昌路73号山西卡乐仕汽服装备有限公司院内左侧底4家 → 山西省太原市小店区大昌路73号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -16026,22 +15610,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16051,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•眉山眉州大道</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -16083,7 +15667,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-1层 → 四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -16127,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -16147,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -16179,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•涪陵迎宾大道</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -16211,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市涪陵区迎宾大道50号 → 重庆市涪陵区迎宾大道50号（临时营业）</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -16243,7 +15827,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -16255,17 +15839,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -16275,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
@@ -16287,17 +15871,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -16307,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -16339,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -16371,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -16403,7 +15987,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -16442,160 +16026,160 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行享界用户中心•上海世纪公园</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号C区 → 上海市浦东新区罗山路1589号A区</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•乌鲁木齐米东汽车城</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区乌鲁木齐市米东区永顺街1695号 → 新疆维吾尔自治区乌鲁木齐市米东区永顺街路1695号</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•张家口胜利路万国汽配城</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市桥东区经济技术开发区张宣大道西侧万国汽配城南行50米 → 河北省张家口市经济开发区胜利南路65号院</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16607,49 +16191,49 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16659,29 +16243,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16691,29 +16275,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16723,29 +16307,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16755,199 +16339,199 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -16959,17 +16543,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16991,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -17018,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -17055,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -17082,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -17114,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -17146,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -17183,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -17215,17 +16799,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -17247,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -17274,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -17311,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -17343,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -17375,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -17407,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17439,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17503,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17530,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17599,17 +17183,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17631,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17663,17 +17247,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17690,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17722,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17754,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17786,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17811,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17843,46 +17427,46 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -17892,22 +17476,22 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
@@ -17919,411 +17503,59 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>蔚来空间 | 成都成双大道</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>蔚来体验中心 | 东营北二路</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>赣州万象城体验店</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>赣州万象城体验店L141</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>地址相似度 70%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>华为授权体验店（东阳新光汇）</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>华为授权体验店（见大未来天地）</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>地址相似度 67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
           <t>店名相似度 84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车东莞麻涌交付中心</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车东莞高埗交付中心</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车长沙君尚零售展厅</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>理想汽车长沙万象城零售中心</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•保定先天下</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•保定北国先天下</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•长春净月</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>1451</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>1452</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1453</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8445</v>
+        <v>8444</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8375</v>
+        <v>8374</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-70</v>
@@ -9808,10 +9808,10 @@
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,14 +15667,14 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -15684,12 +15684,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16122,22 +16122,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16954,22 +16954,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17338,22 +17338,22 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（42家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（112家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（75条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（42家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（112家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（75条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15482,22 +15482,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15940,12 +15940,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16154,22 +16154,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16442,7 +16442,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -16452,12 +16452,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16954,22 +16954,22 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17348,12 +17348,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17466,22 +17466,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,14 +15187,14 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -15204,12 +15204,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,14 +15987,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,29 +16051,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16122,22 +16122,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16314,22 +16314,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16964,12 +16964,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,29 +17427,29 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17530,22 +17530,22 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（42家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（112家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（75条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（42家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（112家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（75条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15482,22 +15482,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -16026,22 +16026,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,14 +16051,14 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,29 +16115,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16314,22 +16314,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16570,22 +16570,22 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（42家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（112家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（75条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（42家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（112家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（75条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
+          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>沙井京基百纳广场一楼橙厅</t>
+          <t>小米汽车交付中心(机场综合楼店)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市宝安区机场综合楼服务中心</t>
+          <t>小米汽车广东深圳宝安区沙井京基百纳</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -12344,12 +12344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车交付中心(机场综合楼店)</t>
+          <t>沙井京基百纳广场一楼橙厅</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期；本期存在高相似店名「小米汽车广东省深圳市宝安区机场综合楼零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15642,22 +15642,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15748,12 +15748,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,14 +15955,14 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -15972,12 +15972,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,14 +15987,14 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16122,22 +16122,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16218,22 +16218,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16506,22 +16506,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16762,22 +16762,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,7 +16986,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -16996,12 +16996,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,29 +15699,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,29 +15763,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,29 +15859,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,14 +16019,14 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,29 +16051,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16762,22 +16762,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,14 +15507,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,14 +15539,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -15556,12 +15556,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,29 +15571,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
@@ -15866,22 +15866,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,29 +15923,29 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,14 +15955,14 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -15972,12 +15972,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,14 +16019,14 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,29 +16051,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,29 +16211,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,29 +17459,29 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>西红门镇金时大街7号院3号楼一层101</t>
+          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>小米汽车北京市大兴区京南运通汽车园销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区迪兴工业园服务中心</t>
+          <t>西红门镇金时大街7号院3号楼一层101</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>成都东安天街城市中心店</t>
+          <t>成都高新宜家家居新能源空间</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
+          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>成都高新宜家家居新能源空间</t>
+          <t>成都东安天街城市中心店</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市武侯区益州大道北段(紧邻三环路天府立交)</t>
+          <t>成都市龙泉驿区桃都大道中段666号A馆1楼30号</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州保利时光里新能源空间</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州保利时光里新能源空间</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市越秀区环市东路332号(建设大马路18号)广州保利时光里一楼</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳星河WORLD.COCO Park新能源空间</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳星河WORLD.COCO Park新能源空间</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区梅坂大道31号</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>苏州吴江吾悦广场新能源空间</t>
+          <t>昆山青阳万达广场新能源空间</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
+          <t>苏州市昆山市青阳北路234号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>昆山青阳万达广场新能源空间</t>
+          <t>苏州吴江吾悦广场新能源空间</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>苏州市昆山市青阳北路234号</t>
+          <t>江苏省苏州市吴江区松陵街道开平路2188号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,29 +15219,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,29 +15379,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,29 +15635,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
@@ -15930,22 +15930,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,29 +15987,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,29 +16147,29 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16314,22 +16314,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 西安金地广场</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 西安金地广场</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16858,22 +16858,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 西安金地广场</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 西安金地广场</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17306,22 +17306,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17466,22 +17466,22 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260629_vs_20260706.xlsx
@@ -11219,7 +11219,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛金狮广场</t>
+          <t>华为授权体验店（融创茂）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
+          <t>山东省青岛市黄岛区滨海大道2777号</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（融创茂）</t>
+          <t>华为智能生活馆•青岛金狮广场</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>山东省青岛市黄岛区滨海大道2777号</t>
+          <t>山东省青岛市崂山区香港东路195号乙青岛金狮广场L1-22+23</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260525，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>广州白云万达新能源空间</t>
+          <t>广州森那美富悦4S中心</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市白云区三元里街道云城东路501号</t>
+          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>广州森那美富悦4S中心</t>
+          <t>广州白云万达新能源空间</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -13240,12 +13240,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广州市花都区迎春路17号自编1栋（厂房五）</t>
+          <t>广东省广州市白云区三元里街道云城东路501号</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>深圳德顺行龙岗卫星店</t>
+          <t>深圳标林卫星店</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
+          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>深圳标林卫星店</t>
+          <t>深圳德顺行龙岗卫星店</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>深圳市福田区沙头街道金城社区红树林路3号联合华鹏竹子林汽车城市展厅二层-B4号</t>
+          <t>深圳市龙岗区中心城长兴北路6号沃尔沃展厅</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海徐汇万科广场</t>
+          <t>蔚来空间 | 上海金桥啦啦宝都</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>上海市徐汇区沪闵路9191号L1-17室</t>
+          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>蔚来空间 | 上海金桥啦啦宝都</t>
+          <t>蔚来空间 | 上海徐汇万科广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区金桥路738号L1-138&amp;139号商铺</t>
+          <t>上海市徐汇区沪闵路9191号L1-17室</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南昌万象城零售中心</t>
+          <t>理想汽车日照东港服务中心（包头路临时店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -15187,29 +15187,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
+          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
         </is>
       </c>
     </row>
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车泉州石狮服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -15251,29 +15251,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -15283,29 +15283,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>郑州宝莲恒汽车销售服务有限公司</t>
+          <t>小鹏汽车泉州石狮服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -15315,29 +15315,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
+          <t>福建省泉州市石狮市狮城大道590号（小鹏汽车泉州南售后服务中心） → 福建省泉州市石狮市狮城大道592号（小鹏汽车泉州石狮服务中心）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车广州黄埔销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -15347,29 +15347,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市温江区光华大道三段1588号1栋合生汇商场1F层L1-44号房屋 → 成都市温江区光华大道三段1588号3栋1F层L1-02号</t>
+          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
+          <t>永康泓宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
+          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
         </is>
       </c>
     </row>
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>长沙瑞宝汽车销售服务有限公司</t>
+          <t>郑州宝莲恒汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -15411,29 +15411,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
+          <t>河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座，邮编: 451450 → 河南省郑州市中牟县郑庵镇中牟汽车产业集聚区轩城大道南、文汇街东、华阳路北、文通路西1期B座</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车黄山屯光大道零售中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
+          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州黄埔销售服务中心</t>
+          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -15475,29 +15475,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广州市黄埔区联和街道南云五路8号自编八栋 → 广州市黄埔区南云五路8号自编八栋</t>
+          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>浙江德奥</t>
+          <t>理想汽车南昌万象城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -15507,29 +15507,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
+          <t>江西省南昌市红谷滩区学府大道388号万象城L117A商铺 → 江西省南昌市学府大道388号万象城L115店铺</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
+          <t>小鹏汽车汕尾大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -15539,29 +15539,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
+          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
+          <t>上汽奥迪永州腾迪用户中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -15571,14 +15571,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>文昌路17号 → 万象城L1-169小米汽车</t>
+          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -15588,12 +15588,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州滨江万象城零售中心</t>
+          <t>浙江德奥</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -15603,29 +15603,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
+          <t>杭州市拱墅区石祥路598号 → 杭州市拱墅区石祥路598-1号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
+          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
         </is>
       </c>
     </row>
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遂宁物流港汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -15667,29 +15667,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>四川省遂宁市遂宁高新区物流港主干道B南侧858-888号 → 四川省遂宁市遂宁高新区物流港物流大道858-888号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1栋 → 浙江省衢州市柯城区浙西大道109号16区1幢</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车新乡红旗服务中心（东安汽车园店）</t>
+          <t>小鹏汽车北京大兴居然之家销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省新乡市红旗区小店镇东安汽车园1号 → 河南省新乡市红旗区小店镇东安汽车园1号（理想汽车售后）</t>
+          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
         </is>
       </c>
     </row>
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
+          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -15731,29 +15731,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
+          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>永康泓宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省永康市烈桥七里经堂康庄路3号, 321300 → 浙江省永康市西城七里经堂330国道边</t>
+          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
         </is>
       </c>
     </row>
@@ -15780,12 +15780,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车汕尾大道销售服务中心</t>
+          <t>小鹏汽车深圳坂田星河COCO PARK销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -15795,29 +15795,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省汕尾市城区红草镇埔边工业区（原汕尾君乐4S店） → 广东省汕尾市城区红草镇海汕公路汕尾市君乐汽车销售服务有限公司</t>
+          <t>广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层A入口 → 广东省深圳市龙岗区坂田街道南坑社区雅宝路1号星河WORLD·COCOPark1层 L1S-038;L1S-039 号商铺</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨龙晟宝锐汽车销售服务有限公司</t>
+          <t>理想汽车温州滨江万象城零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -15827,29 +15827,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道外区先锋路副18号 → 黑龙江省哈尔滨市道外区团结镇先锋路与堤顶路交接处附近</t>
+          <t>浙江省温州市鹿城区滨江街道瓯江路3999号万象城L103号理想汽车 → 浙江省-温州市-鹿城区-滨江街道浦东社区瓯江路3999号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>长沙瑞宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北小鹏汽车服务中心 → 山东省菏泽市定陶区汽车小镇东门向北300米</t>
+          <t>湖南省长沙市雨花区长沙大道688号 邮编410014 → 湖南省长沙市雨花区长沙大道688号</t>
         </is>
       </c>
     </row>
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车孝感仙女湖汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -15891,29 +15891,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>湖北省孝感市孝南区仙女湖路118号 → 湖北省孝感市孝南经济开发区仙女湖路118号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>理想汽车黄山屯光大道零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>武汉市江岸区黄浦科技园特6号 → 江岸区石桥一路10号</t>
+          <t>黄山屯光大道8号 → 黄山屯光大道12号</t>
         </is>
       </c>
     </row>
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京大兴居然之家销售展厅</t>
+          <t>小鹏汽车宿迁双庄汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -15955,29 +15955,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>北京市大兴区枣园路8号居然之家 → 北京市大兴区枣园路8号居然之家大兴店内一层东侧</t>
+          <t>江苏省宿迁市双庄国际汽车城(风驰路西向南100米) → 江苏省宿迁市宿城区双庄国际汽车城(风驰路西向南100米)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪永州腾迪用户中心</t>
+          <t>小米之家广西柳州市鱼峰区柳州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排 → 湖南省永州市零陵区潇湘汽车城西区第一排</t>
+          <t>文昌路17号 → 万象城L1-169小米汽车</t>
         </is>
       </c>
     </row>
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车日照东港服务中心（包头路临时店）</t>
+          <t>理想汽车宜春袁州服务中心（经发大道临时店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -16019,29 +16019,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>山东省日照市东港区奎山汽车城和阳南路与大同路交汇 → 山东省日照市东港区奎山汽车城和阳南路与秦皇岛路交叉口东北180米</t>
+          <t>江西省宜春市袁州区经济技术开发区北春顺路二百米 → 江西省宜春市袁州区经济技术开发区经发大道15号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心</t>
+          <t>理想汽车松原前郭经开零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
+          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
         </is>
       </c>
     </row>
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -16083,29 +16083,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车松原前郭经开零售中心 → 理想汽车松原前郭经开零售展厅</t>
+          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -16115,29 +16115,29 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
+          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
+          <t>小米汽车江西省南昌市新建区望城交付中心 → 小米汽车江西省南昌市新建区望城服务中心</t>
         </is>
       </c>
     </row>
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅</t>
+          <t>理想汽车景德镇国大汽车城零售展厅</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -16179,29 +16179,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车嘉兴海宁银泰城零售展厅 → 理想汽车嘉兴海宁银泰城零售中心</t>
+          <t>理想汽车景德镇国大汽车城零售展厅 → 理想汽车景德镇国大汽车城零售中心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心</t>
+          <t>理想汽车滨州北海大道汽车城零售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠琶洲保利广场销售中心 → 小鹏汽车广州海珠琶洲保利广场销售展厅</t>
+          <t>理想汽车滨州北海大道汽车城零售中心 → 理想汽车滨州北海大道汽车城零售展厅</t>
         </is>
       </c>
     </row>
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 长春世界里</t>
+          <t>蔚来空间 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 长春世界里</t>
+          <t>蔚来体验中心 | 韶关韶南大道</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 遵义国际汽车城</t>
+          <t>蔚来空间 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 遵义国际汽车城</t>
+          <t>蔚来体验中心 | 哈尔滨西城红场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 哈尔滨西城红场</t>
+          <t>宜兴东方沃邦卫星店（过渡运营）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨西城红场</t>
+          <t>宜兴东方沃邦卫星店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -16314,22 +16314,22 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
+          <t>蔚来空间 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
+          <t>蔚来体验中心 | 蚌埠银泰</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -16346,22 +16346,22 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 石家庄万象城</t>
+          <t>小鹏汽车徐州新沂开发区销售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 石家庄万象城</t>
+          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店（过渡运营）</t>
+          <t>蔚来中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>宜兴东方沃邦卫星店</t>
+          <t>蔚来体验中心 | 宁波明州里</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂开发区销售展厅</t>
+          <t>蔚来中心 | 太原万象城</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州新沂吾悦销售展厅</t>
+          <t>蔚来体验中心 | 太原万象城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16442,22 +16442,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 韶关韶南大道</t>
+          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 韶关韶南大道</t>
+          <t>理想汽车杭州上城授权服务中心（信原店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 杭州萧山汽车城</t>
+          <t>蔚来中心 | 长春世界里</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 杭州萧山汽车城</t>
+          <t>蔚来体验中心 | 长春世界里</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 哈尔滨道里</t>
+          <t>蔚来空间 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 哈尔滨道里</t>
+          <t>蔚来体验中心 | 南通海门三和汽车城</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路</t>
+          <t>蔚来中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 东营北二路汽车城</t>
+          <t>蔚来体验中心 | 石家庄万象城</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都成双大道</t>
+          <t>蔚来空间 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都成双大道</t>
+          <t>蔚来体验中心 | 大理丰赢汽车城</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞4S中心</t>
+          <t>蔚来空间 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>武汉建银富瑞维修中心</t>
+          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都锦宸天街</t>
+          <t>蔚来中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙湖锦宸天街</t>
+          <t>蔚来体验中心 | 重庆中央公园</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -16666,22 +16666,22 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
+          <t>武汉建银富瑞4S中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
+          <t>武汉建银富瑞维修中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 蚌埠银泰</t>
+          <t>蔚来中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 蚌埠银泰</t>
+          <t>蔚来体验中心 | 哈尔滨道里</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 广州汉溪长隆</t>
+          <t>理想汽车天津西青授权钣喷中心（盛德宝店）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州汉溪长隆</t>
+          <t>理想汽车天津西青授权服务中心（盛德宝店）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -16762,22 +16762,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 珠海万象汇</t>
+          <t>甘肃中盛奥华汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 珠海万象汇</t>
+          <t>天水国奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>蔚来空间 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
+          <t>蔚来体验中心 | 遵义国际汽车城</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城服务中心（石祥东路店）</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>理想汽车杭州上城授权服务中心（信原店）</t>
+          <t>小米汽车重庆市两江新区龙湖爱加星悦荟</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>蔚来空间 | 成都锦宸天街</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>蔚来空间 | 成都龙湖锦宸天街</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 南通海门三和汽车城</t>
+          <t>蔚来中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 南通海门三和汽车城</t>
+          <t>蔚来体验中心 | 广州汉溪长隆</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 重庆中央公园</t>
+          <t>蔚来空间 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 重庆中央公园</t>
+          <t>蔚来体验中心 | 昆明宜家荟聚</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -16986,22 +16986,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
+          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰服务中心（西江路店）</t>
+          <t>蔚来体验中心 | 东营北二路</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>理想汽车柳州鱼峰授权服务中心（俊汇店）</t>
+          <t>蔚来体验中心 | 东营北二路汽车城</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
+          <t>蔚来空间 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>理想汽车德州德城授权服务中心（驿通店）</t>
+          <t>蔚来体验中心 | 濮阳瑞璞汽车小镇</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 兰州黄河之滨</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 兰州黄河之滨</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 昆明宜家荟聚</t>
+          <t>蔚来中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 昆明宜家荟聚</t>
+          <t>蔚来体验中心 | 兰州黄河之滨</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
+          <t>理想汽车德州德城授权钣喷中心（驿通店）</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车浏阳西环路销售展厅</t>
+          <t>理想汽车德州德城授权服务中心（驿通店）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥华汽车销售服务有限公司</t>
+          <t>蔚来空间 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>天水国奥达汽车销售服务有限公司</t>
+          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 大理丰赢汽车城</t>
+          <t>蔚来空间 | 成都成双大道</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 大理丰赢汽车城</t>
+          <t>蔚来体验中心 | 成都成双大道</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 成都龙潭寺汽车城</t>
+          <t>小鹏汽车长沙浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 成都龙潭寺汽车城</t>
+          <t>小鹏汽车浏阳西环路销售展厅</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 宁波明州里</t>
+          <t>蔚来空间 | 珠海万象汇</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 宁波明州里</t>
+          <t>蔚来体验中心 | 珠海万象汇</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 太原万象城</t>
+          <t>蔚来中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 太原万象城</t>
+          <t>蔚来体验中心 | 上海宝杨宝龙广场</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 仁怀酒都方圆荟</t>
+          <t>蔚来空间 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 仁怀酒都方圆荟</t>
+          <t>蔚来体验中心 | 杭州萧山汽车城</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店</t>
+          <t>华为授权体验店（东阳新光汇）</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>赣州万象城体验店L141</t>
+          <t>华为授权体验店（见大未来天地）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17395,29 +17395,29 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 70%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东阳新光汇）</t>
+          <t>赣州万象城体验店</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（见大未来天地）</t>
+          <t>赣州万象城体验店L141</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 70%</t>
         </is>
       </c>
     </row>
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙君尚零售展厅</t>
+          <t>理想汽车东莞麻涌交付中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙万象城零售中心</t>
+          <t>理想汽车东莞高埗交付中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 75%</t>
         </is>
       </c>
     </row>
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞麻涌交付中心</t>
+          <t>理想汽车长沙君尚零售展厅</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>理想汽车东莞高埗交付中心</t>
+          <t>理想汽车长沙万象城零售中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -17491,29 +17491,29 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 75%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
+          <t>华为智能生活馆•保定先天下</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>华为智能生活馆•保定北国先天下</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -17523,29 +17523,29 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定先天下</t>
+          <t>小米汽车河南省郑州市高新区郑州正弘汇</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•保定北国先天下</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
